--- a/data/b2_primavera/B2 Primavera 02-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 02-2026.xlsx
@@ -4474,25 +4474,25 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>459.95</v>
+        <v>457.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>1651.58</v>
+        <v>58296.66</v>
       </c>
     </row>
     <row r="4">
@@ -4501,52 +4501,52 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>58076.62</v>
+        <v>1838.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>4012.48</v>
+        <v>1879.18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46063</v>
+        <v>46061</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>14000</v>
+        <v>3890.82</v>
       </c>
     </row>
     <row r="7">
@@ -4555,52 +4555,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3600</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1145.8</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1650.03</v>
+        <v>1165.37</v>
       </c>
     </row>
     <row r="10">
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>9585.950000000001</v>
+        <v>10370.14</v>
       </c>
     </row>
     <row r="11">
@@ -4627,16 +4627,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1832.43</v>
+        <v>1441.71</v>
       </c>
     </row>
     <row r="12">
@@ -4645,34 +4645,34 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1585.81</v>
+        <v>3929.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46068</v>
+        <v>46070</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3856.74</v>
+        <v>1781.85</v>
       </c>
     </row>
     <row r="14">
@@ -4690,12 +4690,12 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>19929.34</v>
+        <v>20036.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46074</v>
+        <v>46075</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -4704,11 +4704,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Limpeza da caixa separadora</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>3701.94</v>
+        <v>3287.16</v>
       </c>
     </row>
     <row r="16">
@@ -4726,12 +4726,12 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3588.07</v>
+        <v>3679.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -4740,11 +4740,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>2115.45</v>
+        <v>977.53</v>
       </c>
     </row>
     <row r="18">
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3330.94</v>
+        <v>3589.75</v>
       </c>
     </row>
   </sheetData>
